--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111369</v>
+        <v>121110042</v>
       </c>
       <c r="B2" t="n">
-        <v>91998</v>
+        <v>91102</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510164</v>
+        <v>510111</v>
       </c>
       <c r="R2" t="n">
-        <v>6514269</v>
+        <v>6514233</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110577</v>
+        <v>121110017</v>
       </c>
       <c r="B3" t="n">
-        <v>91092</v>
+        <v>57504</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510177</v>
+        <v>510092</v>
       </c>
       <c r="R3" t="n">
-        <v>6514295</v>
+        <v>6514250</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121110017</v>
+        <v>121111635</v>
       </c>
       <c r="B4" t="n">
-        <v>57501</v>
+        <v>91102</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,13 +939,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510092</v>
+        <v>510044</v>
       </c>
       <c r="R4" t="n">
-        <v>6514250</v>
+        <v>6514260</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121111910</v>
+        <v>121111369</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>92008</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509792</v>
+        <v>510164</v>
       </c>
       <c r="R5" t="n">
-        <v>6514355</v>
+        <v>6514269</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111635</v>
+        <v>121111910</v>
       </c>
       <c r="B6" t="n">
-        <v>91092</v>
+        <v>5169</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510044</v>
+        <v>509792</v>
       </c>
       <c r="R6" t="n">
-        <v>6514260</v>
+        <v>6514355</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121110042</v>
+        <v>121110577</v>
       </c>
       <c r="B7" t="n">
-        <v>91092</v>
+        <v>91102</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510111</v>
+        <v>510177</v>
       </c>
       <c r="R7" t="n">
-        <v>6514233</v>
+        <v>6514295</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,7 +1350,7 @@
         <v>121111726</v>
       </c>
       <c r="B8" t="n">
-        <v>57364</v>
+        <v>57367</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121110042</v>
+        <v>121110577</v>
       </c>
       <c r="B2" t="n">
         <v>91102</v>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510111</v>
+        <v>510177</v>
       </c>
       <c r="R2" t="n">
-        <v>6514233</v>
+        <v>6514295</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110017</v>
+        <v>121110042</v>
       </c>
       <c r="B3" t="n">
-        <v>57504</v>
+        <v>91102</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510092</v>
+        <v>510111</v>
       </c>
       <c r="R3" t="n">
-        <v>6514250</v>
+        <v>6514233</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111635</v>
+        <v>121111726</v>
       </c>
       <c r="B4" t="n">
-        <v>91102</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510044</v>
+        <v>510036</v>
       </c>
       <c r="R4" t="n">
-        <v>6514260</v>
+        <v>6514261</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121110577</v>
+        <v>121110017</v>
       </c>
       <c r="B7" t="n">
-        <v>91102</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510177</v>
+        <v>510092</v>
       </c>
       <c r="R7" t="n">
-        <v>6514295</v>
+        <v>6514250</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121111726</v>
+        <v>121111635</v>
       </c>
       <c r="B8" t="n">
-        <v>57367</v>
+        <v>91102</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1387,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510036</v>
+        <v>510044</v>
       </c>
       <c r="R8" t="n">
-        <v>6514261</v>
+        <v>6514260</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121110577</v>
+        <v>121111726</v>
       </c>
       <c r="B2" t="n">
-        <v>91102</v>
+        <v>57367</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510177</v>
+        <v>510036</v>
       </c>
       <c r="R2" t="n">
-        <v>6514295</v>
+        <v>6514261</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110042</v>
+        <v>121111369</v>
       </c>
       <c r="B3" t="n">
-        <v>91102</v>
+        <v>92020</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>5966</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510111</v>
+        <v>510164</v>
       </c>
       <c r="R3" t="n">
-        <v>6514233</v>
+        <v>6514269</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111726</v>
+        <v>121110042</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>91114</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510036</v>
+        <v>510111</v>
       </c>
       <c r="R4" t="n">
-        <v>6514261</v>
+        <v>6514233</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121111369</v>
+        <v>121111910</v>
       </c>
       <c r="B5" t="n">
-        <v>92008</v>
+        <v>5169</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5966</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510164</v>
+        <v>509792</v>
       </c>
       <c r="R5" t="n">
-        <v>6514269</v>
+        <v>6514355</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111910</v>
+        <v>121111635</v>
       </c>
       <c r="B6" t="n">
-        <v>5169</v>
+        <v>91114</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>509792</v>
+        <v>510044</v>
       </c>
       <c r="R6" t="n">
-        <v>6514355</v>
+        <v>6514260</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121110017</v>
+        <v>121110577</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>91114</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5420</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510092</v>
+        <v>510177</v>
       </c>
       <c r="R7" t="n">
-        <v>6514250</v>
+        <v>6514295</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121111635</v>
+        <v>121110017</v>
       </c>
       <c r="B8" t="n">
-        <v>91102</v>
+        <v>57504</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510044</v>
+        <v>510092</v>
       </c>
       <c r="R8" t="n">
-        <v>6514260</v>
+        <v>6514250</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111726</v>
+        <v>121110042</v>
       </c>
       <c r="B2" t="n">
-        <v>57367</v>
+        <v>91115</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510036</v>
+        <v>510111</v>
       </c>
       <c r="R2" t="n">
-        <v>6514261</v>
+        <v>6514233</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -790,7 +790,7 @@
         <v>121111369</v>
       </c>
       <c r="B3" t="n">
-        <v>92020</v>
+        <v>92021</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121110042</v>
+        <v>121111726</v>
       </c>
       <c r="B4" t="n">
-        <v>91114</v>
+        <v>57367</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510111</v>
+        <v>510036</v>
       </c>
       <c r="R4" t="n">
-        <v>6514233</v>
+        <v>6514261</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121111910</v>
+        <v>121111635</v>
       </c>
       <c r="B5" t="n">
-        <v>5169</v>
+        <v>91115</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>509792</v>
+        <v>510044</v>
       </c>
       <c r="R5" t="n">
-        <v>6514355</v>
+        <v>6514260</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111635</v>
+        <v>121110577</v>
       </c>
       <c r="B6" t="n">
-        <v>91114</v>
+        <v>91115</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510044</v>
+        <v>510177</v>
       </c>
       <c r="R6" t="n">
-        <v>6514260</v>
+        <v>6514295</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121110577</v>
+        <v>121110017</v>
       </c>
       <c r="B7" t="n">
-        <v>91114</v>
+        <v>57504</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510177</v>
+        <v>510092</v>
       </c>
       <c r="R7" t="n">
-        <v>6514295</v>
+        <v>6514250</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121110017</v>
+        <v>121111910</v>
       </c>
       <c r="B8" t="n">
-        <v>57504</v>
+        <v>5169</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510092</v>
+        <v>509792</v>
       </c>
       <c r="R8" t="n">
-        <v>6514250</v>
+        <v>6514355</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121110042</v>
+        <v>121111910</v>
       </c>
       <c r="B2" t="n">
-        <v>91115</v>
+        <v>5172</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5420</v>
+        <v>100526</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510111</v>
+        <v>509792</v>
       </c>
       <c r="R2" t="n">
-        <v>6514233</v>
+        <v>6514355</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121111369</v>
+        <v>121110042</v>
       </c>
       <c r="B3" t="n">
-        <v>92021</v>
+        <v>91118</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510164</v>
+        <v>510111</v>
       </c>
       <c r="R3" t="n">
-        <v>6514269</v>
+        <v>6514233</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,7 +902,7 @@
         <v>121111726</v>
       </c>
       <c r="B4" t="n">
-        <v>57367</v>
+        <v>57370</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121111635</v>
+        <v>121110577</v>
       </c>
       <c r="B5" t="n">
-        <v>91115</v>
+        <v>91118</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510044</v>
+        <v>510177</v>
       </c>
       <c r="R5" t="n">
-        <v>6514260</v>
+        <v>6514295</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121110577</v>
+        <v>121111635</v>
       </c>
       <c r="B6" t="n">
-        <v>91115</v>
+        <v>91118</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510177</v>
+        <v>510044</v>
       </c>
       <c r="R6" t="n">
-        <v>6514295</v>
+        <v>6514260</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121110017</v>
+        <v>121111369</v>
       </c>
       <c r="B7" t="n">
-        <v>57504</v>
+        <v>92024</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103021</v>
+        <v>5966</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1275,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510092</v>
+        <v>510164</v>
       </c>
       <c r="R7" t="n">
-        <v>6514250</v>
+        <v>6514269</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121111910</v>
+        <v>121110017</v>
       </c>
       <c r="B8" t="n">
-        <v>5169</v>
+        <v>57507</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509792</v>
+        <v>510092</v>
       </c>
       <c r="R8" t="n">
-        <v>6514355</v>
+        <v>6514250</v>
       </c>
       <c r="S8" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111910</v>
+        <v>121111369</v>
       </c>
       <c r="B2" t="n">
-        <v>5172</v>
+        <v>92024</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100526</v>
+        <v>5966</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>509792</v>
+        <v>510164</v>
       </c>
       <c r="R2" t="n">
-        <v>6514355</v>
+        <v>6514269</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110042</v>
+        <v>121110017</v>
       </c>
       <c r="B3" t="n">
-        <v>91118</v>
+        <v>57507</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5420</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,13 +827,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510111</v>
+        <v>510092</v>
       </c>
       <c r="R3" t="n">
-        <v>6514233</v>
+        <v>6514250</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121111726</v>
+        <v>121110042</v>
       </c>
       <c r="B4" t="n">
-        <v>57370</v>
+        <v>91118</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510036</v>
+        <v>510111</v>
       </c>
       <c r="R4" t="n">
-        <v>6514261</v>
+        <v>6514233</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121111369</v>
+        <v>121111726</v>
       </c>
       <c r="B7" t="n">
-        <v>92024</v>
+        <v>57370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5966</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510164</v>
+        <v>510036</v>
       </c>
       <c r="R7" t="n">
-        <v>6514269</v>
+        <v>6514261</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1347,10 +1347,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121110017</v>
+        <v>121111910</v>
       </c>
       <c r="B8" t="n">
-        <v>57507</v>
+        <v>5172</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1359,25 +1359,25 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,13 +1387,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>510092</v>
+        <v>509792</v>
       </c>
       <c r="R8" t="n">
-        <v>6514250</v>
+        <v>6514355</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1422,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD8" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1457,6 +1457,566 @@
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>121665334</v>
+      </c>
+      <c r="B9" t="n">
+        <v>91125</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lomgölsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>510101</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6514250</v>
+      </c>
+      <c r="S9" t="n">
+        <v>20</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>121665340</v>
+      </c>
+      <c r="B10" t="n">
+        <v>94770</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2170</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Dicranum flagellare</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Hedw.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lomgölsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>509868</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6514461</v>
+      </c>
+      <c r="S10" t="n">
+        <v>20</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>10:18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>121665330</v>
+      </c>
+      <c r="B11" t="n">
+        <v>91996</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lomgölsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>509935</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6514273</v>
+      </c>
+      <c r="S11" t="n">
+        <v>20</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>121665331</v>
+      </c>
+      <c r="B12" t="n">
+        <v>91996</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Lomgölsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>510102</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6514253</v>
+      </c>
+      <c r="S12" t="n">
+        <v>20</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>11:53</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>121665337</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91996</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lomgölsmossen, Ög</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>509994</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6514448</v>
+      </c>
+      <c r="S13" t="n">
+        <v>20</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-12-18</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>10:36</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Staffan Carlsson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -1462,7 +1462,7 @@
         <v>121665334</v>
       </c>
       <c r="B9" t="n">
-        <v>91125</v>
+        <v>91133</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121665340</v>
+        <v>121665337</v>
       </c>
       <c r="B10" t="n">
-        <v>94770</v>
+        <v>92004</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509868</v>
+        <v>509994</v>
       </c>
       <c r="R10" t="n">
-        <v>6514461</v>
+        <v>6514448</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1686,7 +1686,7 @@
         <v>121665330</v>
       </c>
       <c r="B11" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121665331</v>
+        <v>121665340</v>
       </c>
       <c r="B12" t="n">
-        <v>91996</v>
+        <v>94778</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510102</v>
+        <v>509868</v>
       </c>
       <c r="R12" t="n">
-        <v>6514253</v>
+        <v>6514461</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121665337</v>
+        <v>121665331</v>
       </c>
       <c r="B13" t="n">
-        <v>91996</v>
+        <v>92004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509994</v>
+        <v>510102</v>
       </c>
       <c r="R13" t="n">
-        <v>6514448</v>
+        <v>6514253</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121665331</v>
+        <v>121665340</v>
       </c>
       <c r="B9" t="n">
-        <v>92004</v>
+        <v>94778</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510102</v>
+        <v>509868</v>
       </c>
       <c r="R9" t="n">
-        <v>6514253</v>
+        <v>6514461</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121665330</v>
+        <v>121665334</v>
       </c>
       <c r="B10" t="n">
-        <v>92004</v>
+        <v>91133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509935</v>
+        <v>510101</v>
       </c>
       <c r="R10" t="n">
-        <v>6514273</v>
+        <v>6514250</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121665337</v>
+        <v>121665331</v>
       </c>
       <c r="B11" t="n">
         <v>92004</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509994</v>
+        <v>510102</v>
       </c>
       <c r="R11" t="n">
-        <v>6514448</v>
+        <v>6514253</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121665340</v>
+        <v>121665330</v>
       </c>
       <c r="B12" t="n">
-        <v>94778</v>
+        <v>92004</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509868</v>
+        <v>509935</v>
       </c>
       <c r="R12" t="n">
-        <v>6514461</v>
+        <v>6514273</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121665334</v>
+        <v>121665337</v>
       </c>
       <c r="B13" t="n">
-        <v>91133</v>
+        <v>92004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510101</v>
+        <v>509994</v>
       </c>
       <c r="R13" t="n">
-        <v>6514250</v>
+        <v>6514448</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121665340</v>
+        <v>121665331</v>
       </c>
       <c r="B9" t="n">
-        <v>94778</v>
+        <v>92004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509868</v>
+        <v>510102</v>
       </c>
       <c r="R9" t="n">
-        <v>6514461</v>
+        <v>6514253</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121665334</v>
+        <v>121665330</v>
       </c>
       <c r="B10" t="n">
-        <v>91133</v>
+        <v>92004</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510101</v>
+        <v>509935</v>
       </c>
       <c r="R10" t="n">
-        <v>6514250</v>
+        <v>6514273</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121665331</v>
+        <v>121665334</v>
       </c>
       <c r="B11" t="n">
-        <v>92004</v>
+        <v>91133</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510102</v>
+        <v>510101</v>
       </c>
       <c r="R11" t="n">
-        <v>6514253</v>
+        <v>6514250</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121665330</v>
+        <v>121665337</v>
       </c>
       <c r="B12" t="n">
         <v>92004</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509935</v>
+        <v>509994</v>
       </c>
       <c r="R12" t="n">
-        <v>6514273</v>
+        <v>6514448</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121665337</v>
+        <v>121665340</v>
       </c>
       <c r="B13" t="n">
-        <v>92004</v>
+        <v>94778</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509994</v>
+        <v>509868</v>
       </c>
       <c r="R13" t="n">
-        <v>6514448</v>
+        <v>6514461</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121665331</v>
+        <v>121665340</v>
       </c>
       <c r="B9" t="n">
-        <v>92004</v>
+        <v>94778</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510102</v>
+        <v>509868</v>
       </c>
       <c r="R9" t="n">
-        <v>6514253</v>
+        <v>6514461</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1795,7 +1795,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121665337</v>
+        <v>121665331</v>
       </c>
       <c r="B12" t="n">
         <v>92004</v>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509994</v>
+        <v>510102</v>
       </c>
       <c r="R12" t="n">
-        <v>6514448</v>
+        <v>6514253</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121665340</v>
+        <v>121665337</v>
       </c>
       <c r="B13" t="n">
-        <v>94778</v>
+        <v>92004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509868</v>
+        <v>509994</v>
       </c>
       <c r="R13" t="n">
-        <v>6514461</v>
+        <v>6514448</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121665340</v>
+        <v>121665337</v>
       </c>
       <c r="B9" t="n">
-        <v>94778</v>
+        <v>92004</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509868</v>
+        <v>509994</v>
       </c>
       <c r="R9" t="n">
-        <v>6514461</v>
+        <v>6514448</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121665330</v>
+        <v>121665340</v>
       </c>
       <c r="B10" t="n">
-        <v>92004</v>
+        <v>94778</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509935</v>
+        <v>509868</v>
       </c>
       <c r="R10" t="n">
-        <v>6514273</v>
+        <v>6514461</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,10 +1683,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121665334</v>
+        <v>121665331</v>
       </c>
       <c r="B11" t="n">
-        <v>91133</v>
+        <v>92004</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1699,21 +1699,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510101</v>
+        <v>510102</v>
       </c>
       <c r="R11" t="n">
-        <v>6514250</v>
+        <v>6514253</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121665331</v>
+        <v>121665334</v>
       </c>
       <c r="B12" t="n">
-        <v>92004</v>
+        <v>91133</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510102</v>
+        <v>510101</v>
       </c>
       <c r="R12" t="n">
-        <v>6514253</v>
+        <v>6514250</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1907,7 +1907,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121665337</v>
+        <v>121665330</v>
       </c>
       <c r="B13" t="n">
         <v>92004</v>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509994</v>
+        <v>509935</v>
       </c>
       <c r="R13" t="n">
-        <v>6514448</v>
+        <v>6514273</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121665340</v>
+        <v>121665331</v>
       </c>
       <c r="B10" t="n">
-        <v>94778</v>
+        <v>92004</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509868</v>
+        <v>510102</v>
       </c>
       <c r="R10" t="n">
-        <v>6514461</v>
+        <v>6514253</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1646,7 +1646,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,7 +1683,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121665331</v>
+        <v>121665330</v>
       </c>
       <c r="B11" t="n">
         <v>92004</v>
@@ -1723,10 +1723,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>510102</v>
+        <v>509935</v>
       </c>
       <c r="R11" t="n">
-        <v>6514253</v>
+        <v>6514273</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121665334</v>
+        <v>121665340</v>
       </c>
       <c r="B12" t="n">
-        <v>91133</v>
+        <v>94778</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5420</v>
+        <v>2170</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510101</v>
+        <v>509868</v>
       </c>
       <c r="R12" t="n">
-        <v>6514250</v>
+        <v>6514461</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121665330</v>
+        <v>121665334</v>
       </c>
       <c r="B13" t="n">
-        <v>92004</v>
+        <v>91133</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509935</v>
+        <v>510101</v>
       </c>
       <c r="R13" t="n">
-        <v>6514273</v>
+        <v>6514250</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -1459,10 +1459,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121665337</v>
+        <v>121665340</v>
       </c>
       <c r="B9" t="n">
-        <v>92004</v>
+        <v>94778</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1475,21 +1475,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>4364</v>
+        <v>2170</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1499,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>509994</v>
+        <v>509868</v>
       </c>
       <c r="R9" t="n">
-        <v>6514448</v>
+        <v>6514461</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1534,7 +1534,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,10 +1571,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121665331</v>
+        <v>121665334</v>
       </c>
       <c r="B10" t="n">
-        <v>92004</v>
+        <v>91133</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1587,21 +1587,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1611,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>510102</v>
+        <v>510101</v>
       </c>
       <c r="R10" t="n">
-        <v>6514253</v>
+        <v>6514250</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1795,10 +1795,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121665340</v>
+        <v>121665331</v>
       </c>
       <c r="B12" t="n">
-        <v>94778</v>
+        <v>92004</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1811,21 +1811,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2170</v>
+        <v>4364</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1835,10 +1835,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>509868</v>
+        <v>510102</v>
       </c>
       <c r="R12" t="n">
-        <v>6514461</v>
+        <v>6514253</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1870,7 +1870,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1880,7 +1880,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1907,10 +1907,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121665334</v>
+        <v>121665337</v>
       </c>
       <c r="B13" t="n">
-        <v>91133</v>
+        <v>92004</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1923,21 +1923,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1947,10 +1947,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>510101</v>
+        <v>509994</v>
       </c>
       <c r="R13" t="n">
-        <v>6514250</v>
+        <v>6514448</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94840</v>
+        <v>94850</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94850</v>
+        <v>94862</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94862</v>
+        <v>94867</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94867</v>
+        <v>94876</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,11 +2036,6 @@
       </c>
       <c r="E14" t="n">
         <v>2170</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Flagellkvastmossa</t>
-        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94876</v>
+        <v>94889</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2036,6 +2036,11 @@
       </c>
       <c r="E14" t="n">
         <v>2170</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Flagellkvastmossa</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94889</v>
+        <v>94902</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94902</v>
+        <v>94904</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94904</v>
+        <v>94905</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2022,7 +2022,7 @@
         <v>122272290</v>
       </c>
       <c r="B14" t="n">
-        <v>94905</v>
+        <v>94908</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2124,6 +2124,127 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>128940120</v>
+      </c>
+      <c r="B15" t="n">
+        <v>56910</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>102613</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Orre</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Lyrurus tetrix</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lomgölen, Ög</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>509868</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6514459</v>
+      </c>
+      <c r="S15" t="n">
+        <v>5</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Motala</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Godegård</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Hördes från norr om Lomgölen.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Tomas Björkesten</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>128940120</v>
       </c>
       <c r="B15" t="n">
-        <v>56910</v>
+        <v>56913</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>128940120</v>
       </c>
       <c r="B15" t="n">
-        <v>56913</v>
+        <v>56916</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>128940120</v>
       </c>
       <c r="B15" t="n">
-        <v>56916</v>
+        <v>56918</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -2129,7 +2129,7 @@
         <v>128940120</v>
       </c>
       <c r="B15" t="n">
-        <v>56918</v>
+        <v>56920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 49715-2024 artfynd.xlsx
+++ b/artfynd/A 49715-2024 artfynd.xlsx
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121111369</v>
+        <v>121665340</v>
       </c>
       <c r="B2" t="n">
-        <v>92024</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5966</v>
+        <v>2170</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lomgölen, Lomgölen, Ög</t>
+          <t>Lomgölsmossen, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>510164</v>
+        <v>509868</v>
       </c>
       <c r="R2" t="n">
-        <v>6514269</v>
+        <v>6514461</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,65 +770,64 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121110017</v>
+        <v>122272290</v>
       </c>
       <c r="B3" t="n">
-        <v>57507</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>2170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Flagellkvastmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dicranum flagellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lomgölen, Lomgölen, Ög</t>
+          <t>Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>510092</v>
+        <v>509868</v>
       </c>
       <c r="R3" t="n">
-        <v>6514250</v>
+        <v>6514459</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -857,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:26</t>
+          <t>2025-01-21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,71 +865,67 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121110042</v>
+        <v>121665330</v>
       </c>
       <c r="B4" t="n">
-        <v>91118</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lomgölen, Lomgölen, Ög</t>
+          <t>Lomgölsmossen, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>510111</v>
+        <v>509935</v>
       </c>
       <c r="R4" t="n">
-        <v>6514233</v>
+        <v>6514273</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -969,22 +949,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>12:02</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -999,65 +979,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121110577</v>
+        <v>121665331</v>
       </c>
       <c r="B5" t="n">
-        <v>91118</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lomgölen, Lomgölen, Ög</t>
+          <t>Lomgölsmossen, Ög</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>510177</v>
+        <v>510102</v>
       </c>
       <c r="R5" t="n">
-        <v>6514295</v>
+        <v>6514253</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1081,22 +1056,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1111,65 +1086,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121111635</v>
+        <v>121665337</v>
       </c>
       <c r="B6" t="n">
-        <v>91118</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5420</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lomgölen, Lomgölen, Ög</t>
+          <t>Lomgölsmossen, Ög</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>510044</v>
+        <v>509994</v>
       </c>
       <c r="R6" t="n">
-        <v>6514260</v>
+        <v>6514448</v>
       </c>
       <c r="S6" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1193,22 +1163,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
+          <t>2024-12-18</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1223,27 +1193,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Staffan Carlsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>121111726</v>
+        <v>128943379</v>
       </c>
       <c r="B7" t="n">
-        <v>57370</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1216,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,13 +1240,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>510036</v>
+        <v>510238</v>
       </c>
       <c r="R7" t="n">
-        <v>6514261</v>
+        <v>6514119</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1305,22 +1270,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2024-11-10</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>12:18</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1335,27 +1290,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Malin Gröndahl Maass</t>
+          <t>Tomas Björkesten</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>121111910</v>
+        <v>121110042</v>
       </c>
       <c r="B8" t="n">
-        <v>5172</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1363,21 +1313,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>5420</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1387,10 +1337,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>509792</v>
+        <v>510111</v>
       </c>
       <c r="R8" t="n">
-        <v>6514355</v>
+        <v>6514233</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1422,7 +1372,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1382,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:43</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,15 +1409,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>121665334</v>
+        <v>121110577</v>
       </c>
       <c r="B9" t="n">
-        <v>91150</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1495,17 +1440,17 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lomgölsmossen, Ög</t>
+          <t>Lomgölen, Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>510101</v>
+        <v>510177</v>
       </c>
       <c r="R9" t="n">
-        <v>6514250</v>
+        <v>6514295</v>
       </c>
       <c r="S9" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1529,22 +1474,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1559,27 +1504,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>121665337</v>
+        <v>121111635</v>
       </c>
       <c r="B10" t="n">
-        <v>92021</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1587,37 +1527,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lomgölsmossen, Ög</t>
+          <t>Lomgölen, Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>509994</v>
+        <v>510044</v>
       </c>
       <c r="R10" t="n">
-        <v>6514448</v>
+        <v>6514260</v>
       </c>
       <c r="S10" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1641,22 +1581,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1671,27 +1611,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>121665330</v>
+        <v>121665334</v>
       </c>
       <c r="B11" t="n">
-        <v>92021</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1634,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1658,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>509935</v>
+        <v>510101</v>
       </c>
       <c r="R11" t="n">
-        <v>6514273</v>
+        <v>6514250</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1758,7 +1693,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1768,7 +1703,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:02</t>
+          <t>11:53</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,53 +1730,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>121665331</v>
+        <v>121111369</v>
       </c>
       <c r="B12" t="n">
-        <v>92021</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93235</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>4364</v>
+        <v>5966</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lomgölsmossen, Ög</t>
+          <t>Lomgölen, Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>510102</v>
+        <v>510164</v>
       </c>
       <c r="R12" t="n">
-        <v>6514253</v>
+        <v>6514269</v>
       </c>
       <c r="S12" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1865,22 +1795,22 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>11:53</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1895,27 +1825,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>121665340</v>
+        <v>121111726</v>
       </c>
       <c r="B13" t="n">
-        <v>94805</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1923,37 +1848,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2170</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lomgölsmossen, Ög</t>
+          <t>Lomgölen, Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>509868</v>
+        <v>510036</v>
       </c>
       <c r="R13" t="n">
-        <v>6514461</v>
+        <v>6514261</v>
       </c>
       <c r="S13" t="n">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1977,22 +1902,22 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2024-12-18</t>
+          <t>2024-11-10</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>10:18</t>
+          <t>12:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2007,27 +1932,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Staffan Carlsson</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122272290</v>
+        <v>121111910</v>
       </c>
       <c r="B14" t="n">
-        <v>94908</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Godkänd. Foto (eller ljud) granskat av validerare</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2035,41 +1955,37 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2170</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Flagellkvastmossa</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dicranum flagellare</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Hedw.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Lomgölen, Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>509868</v>
+        <v>509792</v>
       </c>
       <c r="R14" t="n">
-        <v>6514459</v>
+        <v>6514355</v>
       </c>
       <c r="S14" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2093,12 +2009,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-01-21</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:43</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2107,86 +2033,66 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128940120</v>
+        <v>121110017</v>
       </c>
       <c r="B15" t="n">
-        <v>56920</v>
+        <v>58114</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>102613</v>
+        <v>103021</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Orre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lyrurus tetrix</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lomgölen, Ög</t>
+          <t>Lomgölen, Lomgölen, Ög</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>509868</v>
+        <v>510092</v>
       </c>
       <c r="R15" t="n">
-        <v>6514459</v>
+        <v>6514250</v>
       </c>
       <c r="S15" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2210,17 +2116,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Hördes från norr om Lomgölen.</t>
+          <t>2024-11-10</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2235,12 +2146,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Tomas Björkesten</t>
+          <t>Malin Gröndahl Maass</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
